--- a/temp/BBVA_VISA_20250228.xlsx
+++ b/temp/BBVA_VISA_20250228.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-938294.62</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-938294,62</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>31549</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>31549,0</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>550</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>550,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>40915.01</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>40915,01</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -571,12 +579,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>8900</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8900,0</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>40000</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>40000,0</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -621,12 +633,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>48200</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>48200,0</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -646,12 +660,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>17600</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>17600,0</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -671,12 +687,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>25069</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>25069,0</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -696,12 +714,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>850</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>850,0</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -721,12 +741,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>37600</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>37600,0</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -746,12 +768,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>249600</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>249600,0</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -771,12 +795,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>9999</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9999,0</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -796,12 +822,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>9500</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9500,0</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -821,12 +849,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>35460</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>35460,0</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -846,12 +876,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>12000</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>12000,0</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -871,12 +903,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>6200</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6200,0</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -896,12 +930,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>4330</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4330,0</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -921,12 +957,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>19300</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>19300,0</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -946,12 +984,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>3619.99</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3619,99</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -971,12 +1011,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>180000</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>180000,0</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -996,12 +1038,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>484538.59</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>484538,59</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1065,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>110575.14</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>110575,14</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1092,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>12500.32</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>12500,32</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1119,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>3900</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3900,0</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1146,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>3700</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3700,0</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1173,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>32698</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>32698,0</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1200,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>9357.040000000001</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>9357,04</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1227,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>24500</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>24500,0</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1254,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>50011</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>50011,0</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1281,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>3299</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3299,0</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1308,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>11400</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>11400,0</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1335,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>1258.41</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1258,41</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1362,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>13422.4</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>13422,4</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1389,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>265.96</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>265,96</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1416,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>2792.58</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2792,58</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1443,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>3989.4</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3989,4</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>

--- a/temp/BBVA_VISA_20250228.xlsx
+++ b/temp/BBVA_VISA_20250228.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>866317K PEDIDOSYA RESTAURANTE</t>
+          <t>PEDIDOSYA RESTAURANTE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>888794K PEDIDOSYA PROPINAS</t>
+          <t>PEDIDOSYA PROPINAS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>022016* PERSONAL FLOW 300060254971003</t>
+          <t>PERSONAL FLOW 300060254971003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>003431* SANDRULI SRL</t>
+          <t>SANDRULI SRL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>934659K MERPAGO*FLORAALMACENN</t>
+          <t>MERPAGO*FLORAALMACENN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>446150K MERPAGO*LEPAINQUOTIDI</t>
+          <t>MERPAGO*LEPAINQUOTIDI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>880557K MERPAGO*RINCONNORTENO</t>
+          <t>MERPAGO*RINCONNORTENO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>024266K PEDIDOSYA RESTAURANTE</t>
+          <t>PEDIDOSYA RESTAURANTE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>044880K PEDIDOSYA PROPINAS</t>
+          <t>PEDIDOSYA PROPINAS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002972* PALMYRA</t>
+          <t>PALMYRA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>983581K MERPAGO*ESCUELADAVINCI</t>
+          <t>MERPAGO*ESCUELADAVINCI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>863303Q NETFLIX.COM 44052516158577642</t>
+          <t>NETFLIX.COM 44052516158577642</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>707658K MERPAGO*SCANNAPIECO</t>
+          <t>MERPAGO*SCANNAPIECO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>592429K MERPAGO*MIFARMA</t>
+          <t>MERPAGO*MIFARMA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>003836* SANDRULI SRL</t>
+          <t>SANDRULI SRL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>988774K MERPAGO*LUCKY13</t>
+          <t>MERPAGO*LUCKY13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>707077K MERPAGO*SUPERDIA</t>
+          <t>MERPAGO*SUPERDIA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>003950* SANDRULI SRL</t>
+          <t>SANDRULI SRL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>003447K AXION BONPLAND</t>
+          <t>AXION BONPLAND</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>569822K MERPAGO*PREMIUMRENTAC</t>
+          <t>MERPAGO*PREMIUMRENTAC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>000071* DESPEGAR</t>
+          <t>DESPEGAR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>389987* JetSmart SpA</t>
+          <t>JetSmart SpA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>993268* BBVA SEGUROS A2052000420510-023-000</t>
+          <t>BBVA SEGUROS A2052000420510-023-000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>869856* PATH</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>361460K MERPAGO*NYRB</t>
+          <t>MERPAGO*NYRB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>290412* MERPAGO*MCDONALDSECOMM</t>
+          <t>MERPAGO*MCDONALDSECOMM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>004188K AXION BONPLAND</t>
+          <t>AXION BONPLAND</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>004319* SANDRULI SRL</t>
+          <t>SANDRULI SRL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>012318* TRIUNFO COOP D0000007681097-094-005</t>
+          <t>TRIUNFO COOP D0000007681097-094-005</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>080904V Spotify</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>007586K MERPAGO*ADORADO</t>
+          <t>MERPAGO*ADORADO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>000001* AUTOPISTAS DEL S 960001911719401</t>
+          <t>AUTOPISTAS DEL S 960001911719401</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>140411* EXPERTA SEGURO0000033489360-015-005</t>
+          <t>EXPERTA SEGURO0000033489360-015-005</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
